--- a/data/england/p3_data_preparation/df_etiquetas.xlsx
+++ b/data/england/p3_data_preparation/df_etiquetas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3170"/>
+  <dimension ref="A1:C2745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41605,6381 +41605,6 @@
         <v>424</v>
       </c>
     </row>
-    <row r="2746">
-      <c r="A2746" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2746" t="inlineStr">
-        <is>
-          <t>adams derek</t>
-        </is>
-      </c>
-      <c r="C2746" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2747">
-      <c r="A2747" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2747" t="inlineStr">
-        <is>
-          <t>adams neil</t>
-        </is>
-      </c>
-      <c r="C2747" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2748">
-      <c r="A2748" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2748" t="inlineStr">
-        <is>
-          <t>adkins nigel</t>
-        </is>
-      </c>
-      <c r="C2748" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2749">
-      <c r="A2749" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2749" t="inlineStr">
-        <is>
-          <t>advocaat dick</t>
-        </is>
-      </c>
-      <c r="C2749" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2750">
-      <c r="A2750" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2750" t="inlineStr">
-        <is>
-          <t>agnew steve</t>
-        </is>
-      </c>
-      <c r="C2750" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2751">
-      <c r="A2751" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2751" t="inlineStr">
-        <is>
-          <t>ainsworth gareth</t>
-        </is>
-      </c>
-      <c r="C2751" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2752">
-      <c r="A2752" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2752" t="inlineStr">
-        <is>
-          <t>alexander graham</t>
-        </is>
-      </c>
-      <c r="C2752" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2753">
-      <c r="A2753" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2753" t="inlineStr">
-        <is>
-          <t>allardyce samuel</t>
-        </is>
-      </c>
-      <c r="C2753" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2754">
-      <c r="A2754" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2754" t="inlineStr">
-        <is>
-          <t>allinson ian</t>
-        </is>
-      </c>
-      <c r="C2754" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2755">
-      <c r="A2755" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2755" t="inlineStr">
-        <is>
-          <t>ancelotti carlo</t>
-        </is>
-      </c>
-      <c r="C2755" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2756">
-      <c r="A2756" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2756" t="inlineStr">
-        <is>
-          <t>appleton michael</t>
-        </is>
-      </c>
-      <c r="C2756" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2757">
-      <c r="A2757" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2757" t="inlineStr">
-        <is>
-          <t>ardley neal</t>
-        </is>
-      </c>
-      <c r="C2757" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2758">
-      <c r="A2758" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2758" t="inlineStr">
-        <is>
-          <t>armstrong alun</t>
-        </is>
-      </c>
-      <c r="C2758" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2759">
-      <c r="A2759" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2759" t="inlineStr">
-        <is>
-          <t>artell david</t>
-        </is>
-      </c>
-      <c r="C2759" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2760">
-      <c r="A2760" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2760" t="inlineStr">
-        <is>
-          <t>arteta mikel</t>
-        </is>
-      </c>
-      <c r="C2760" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2761">
-      <c r="A2761" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2761" t="inlineStr">
-        <is>
-          <t>arveladze shota</t>
-        </is>
-      </c>
-      <c r="C2761" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2762">
-      <c r="A2762" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2762" t="inlineStr">
-        <is>
-          <t>asbaghi poya</t>
-        </is>
-      </c>
-      <c r="C2762" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2763">
-      <c r="A2763" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2763" t="inlineStr">
-        <is>
-          <t>askey john</t>
-        </is>
-      </c>
-      <c r="C2763" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2764">
-      <c r="A2764" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2764" t="inlineStr">
-        <is>
-          <t>banide laurent</t>
-        </is>
-      </c>
-      <c r="C2764" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2765">
-      <c r="A2765" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2765" t="inlineStr">
-        <is>
-          <t>barrett adam</t>
-        </is>
-      </c>
-      <c r="C2765" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2766">
-      <c r="A2766" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2766" t="inlineStr">
-        <is>
-          <t>barrow graham</t>
-        </is>
-      </c>
-      <c r="C2766" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2767">
-      <c r="A2767" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2767" t="inlineStr">
-        <is>
-          <t>barry murphy brian</t>
-        </is>
-      </c>
-      <c r="C2767" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2768">
-      <c r="A2768" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2768" t="inlineStr">
-        <is>
-          <t>barton joey</t>
-        </is>
-      </c>
-      <c r="C2768" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2769">
-      <c r="A2769" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2769" t="inlineStr">
-        <is>
-          <t>bassey simon</t>
-        </is>
-      </c>
-      <c r="C2769" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2770">
-      <c r="A2770" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2770" t="inlineStr">
-        <is>
-          <t>beale michael</t>
-        </is>
-      </c>
-      <c r="C2770" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2771">
-      <c r="A2771" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2771" t="inlineStr">
-        <is>
-          <t>beale richard</t>
-        </is>
-      </c>
-      <c r="C2771" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2772">
-      <c r="A2772" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2772" t="inlineStr">
-        <is>
-          <t>beech chris</t>
-        </is>
-      </c>
-      <c r="C2772" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2773">
-      <c r="A2773" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2773" t="inlineStr">
-        <is>
-          <t>bell lee</t>
-        </is>
-      </c>
-      <c r="C2773" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2774">
-      <c r="A2774" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2774" t="inlineStr">
-        <is>
-          <t>benitez rafael</t>
-        </is>
-      </c>
-      <c r="C2774" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2775">
-      <c r="A2775" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2775" t="inlineStr">
-        <is>
-          <t>bentley jim</t>
-        </is>
-      </c>
-      <c r="C2775" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2776">
-      <c r="A2776" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2776" t="inlineStr">
-        <is>
-          <t>bentley mark</t>
-        </is>
-      </c>
-      <c r="C2776" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2777">
-      <c r="A2777" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2777" t="inlineStr">
-        <is>
-          <t>bielsa marcelo</t>
-        </is>
-      </c>
-      <c r="C2777" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2778">
-      <c r="A2778" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2778" t="inlineStr">
-        <is>
-          <t>bilic slaven</t>
-        </is>
-      </c>
-      <c r="C2778" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2779">
-      <c r="A2779" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2779" t="inlineStr">
-        <is>
-          <t>black eric</t>
-        </is>
-      </c>
-      <c r="C2779" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2780">
-      <c r="A2780" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2780" t="inlineStr">
-        <is>
-          <t>bloomfield matt</t>
-        </is>
-      </c>
-      <c r="C2780" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2781">
-      <c r="A2781" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2781" t="inlineStr">
-        <is>
-          <t>boa morte luis</t>
-        </is>
-      </c>
-      <c r="C2781" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2782">
-      <c r="A2782" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2782" t="inlineStr">
-        <is>
-          <t>bonner mark</t>
-        </is>
-      </c>
-      <c r="C2782" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2783">
-      <c r="A2783" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2783" t="inlineStr">
-        <is>
-          <t>bould steve</t>
-        </is>
-      </c>
-      <c r="C2783" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2784">
-      <c r="A2784" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2784" t="inlineStr">
-        <is>
-          <t>bowen mark</t>
-        </is>
-      </c>
-      <c r="C2784" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2785">
-      <c r="A2785" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2785" t="inlineStr">
-        <is>
-          <t>bowyer gary</t>
-        </is>
-      </c>
-      <c r="C2785" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2786">
-      <c r="A2786" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2786" t="inlineStr">
-        <is>
-          <t>bowyer lee</t>
-        </is>
-      </c>
-      <c r="C2786" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2787">
-      <c r="A2787" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2787" t="inlineStr">
-        <is>
-          <t>bradley bob</t>
-        </is>
-      </c>
-      <c r="C2787" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2788">
-      <c r="A2788" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2788" t="inlineStr">
-        <is>
-          <t>brady jon</t>
-        </is>
-      </c>
-      <c r="C2788" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2789">
-      <c r="A2789" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2789" t="inlineStr">
-        <is>
-          <t>brannan ged</t>
-        </is>
-      </c>
-      <c r="C2789" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2790">
-      <c r="A2790" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2790" t="inlineStr">
-        <is>
-          <t>brazil gary</t>
-        </is>
-      </c>
-      <c r="C2790" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2791">
-      <c r="A2791" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2791" t="inlineStr">
-        <is>
-          <t>breitenreiter andre</t>
-        </is>
-      </c>
-      <c r="C2791" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2792">
-      <c r="A2792" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2792" t="inlineStr">
-        <is>
-          <t>brennan dean</t>
-        </is>
-      </c>
-      <c r="C2792" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2793">
-      <c r="A2793" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2793" t="inlineStr">
-        <is>
-          <t>britton leon</t>
-        </is>
-      </c>
-      <c r="C2793" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2794">
-      <c r="A2794" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2794" t="inlineStr">
-        <is>
-          <t>brown phil</t>
-        </is>
-      </c>
-      <c r="C2794" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2795">
-      <c r="A2795" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2795" t="inlineStr">
-        <is>
-          <t>brown scott</t>
-        </is>
-      </c>
-      <c r="C2795" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2796">
-      <c r="A2796" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2796" t="inlineStr">
-        <is>
-          <t>brown wayne</t>
-        </is>
-      </c>
-      <c r="C2796" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2797">
-      <c r="A2797" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2797" t="inlineStr">
-        <is>
-          <t>bruce steve</t>
-        </is>
-      </c>
-      <c r="C2797" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2798">
-      <c r="A2798" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2798" t="inlineStr">
-        <is>
-          <t>buckingham des</t>
-        </is>
-      </c>
-      <c r="C2798" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2799">
-      <c r="A2799" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2799" t="inlineStr">
-        <is>
-          <t>bullen lee</t>
-        </is>
-      </c>
-      <c r="C2799" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2800">
-      <c r="A2800" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2800" t="inlineStr">
-        <is>
-          <t>bulut erol</t>
-        </is>
-      </c>
-      <c r="C2800" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2801">
-      <c r="A2801" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2801" t="inlineStr">
-        <is>
-          <t>burchnall ian</t>
-        </is>
-      </c>
-      <c r="C2801" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2802">
-      <c r="A2802" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2802" t="inlineStr">
-        <is>
-          <t>calderwood colin</t>
-        </is>
-      </c>
-      <c r="C2802" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2803">
-      <c r="A2803" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2803" t="inlineStr">
-        <is>
-          <t>caldwell gary</t>
-        </is>
-      </c>
-      <c r="C2803" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2804">
-      <c r="A2804" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2804" t="inlineStr">
-        <is>
-          <t>carlisle wayne</t>
-        </is>
-      </c>
-      <c r="C2804" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2805">
-      <c r="A2805" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2805" t="inlineStr">
-        <is>
-          <t>carrick michael</t>
-        </is>
-      </c>
-      <c r="C2805" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="2806">
-      <c r="A2806" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2806" t="inlineStr">
-        <is>
-          <t>carsley lee</t>
-        </is>
-      </c>
-      <c r="C2806" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2807">
-      <c r="A2807" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2807" t="inlineStr">
-        <is>
-          <t>carvalhal carlos</t>
-        </is>
-      </c>
-      <c r="C2807" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2808">
-      <c r="A2808" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2808" t="inlineStr">
-        <is>
-          <t>carver john</t>
-        </is>
-      </c>
-      <c r="C2808" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2809">
-      <c r="A2809" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2809" t="inlineStr">
-        <is>
-          <t>challinor dave</t>
-        </is>
-      </c>
-      <c r="C2809" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2810">
-      <c r="A2810" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2810" t="inlineStr">
-        <is>
-          <t>christiansen thomas</t>
-        </is>
-      </c>
-      <c r="C2810" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2811">
-      <c r="A2811" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2811" t="inlineStr">
-        <is>
-          <t>cifuentes marti</t>
-        </is>
-      </c>
-      <c r="C2811" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2812">
-      <c r="A2812" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2812" t="inlineStr">
-        <is>
-          <t>clark lee</t>
-        </is>
-      </c>
-      <c r="C2812" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2813">
-      <c r="A2813" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2813" t="inlineStr">
-        <is>
-          <t>clarke darrell</t>
-        </is>
-      </c>
-      <c r="C2813" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2814">
-      <c r="A2814" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2814" t="inlineStr">
-        <is>
-          <t>clarke steve</t>
-        </is>
-      </c>
-      <c r="C2814" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2815">
-      <c r="A2815" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2815" t="inlineStr">
-        <is>
-          <t>clement paul</t>
-        </is>
-      </c>
-      <c r="C2815" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2816">
-      <c r="A2816" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2816" t="inlineStr">
-        <is>
-          <t>clotet pep</t>
-        </is>
-      </c>
-      <c r="C2816" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2817">
-      <c r="A2817" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2817" t="inlineStr">
-        <is>
-          <t>clough nigel</t>
-        </is>
-      </c>
-      <c r="C2817" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2818">
-      <c r="A2818" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2818" t="inlineStr">
-        <is>
-          <t>cocu phillip</t>
-        </is>
-      </c>
-      <c r="C2818" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2819">
-      <c r="A2819" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2819" t="inlineStr">
-        <is>
-          <t>coleman chris</t>
-        </is>
-      </c>
-      <c r="C2819" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2820">
-      <c r="A2820" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2820" t="inlineStr">
-        <is>
-          <t>coleman john</t>
-        </is>
-      </c>
-      <c r="C2820" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2821">
-      <c r="A2821" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2821" t="inlineStr">
-        <is>
-          <t>connor terry</t>
-        </is>
-      </c>
-      <c r="C2821" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2822">
-      <c r="A2822" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2822" t="inlineStr">
-        <is>
-          <t>conte antonio</t>
-        </is>
-      </c>
-      <c r="C2822" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2823">
-      <c r="A2823" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2823" t="inlineStr">
-        <is>
-          <t>cook paul</t>
-        </is>
-      </c>
-      <c r="C2823" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2824">
-      <c r="A2824" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2824" t="inlineStr">
-        <is>
-          <t>cooper mark</t>
-        </is>
-      </c>
-      <c r="C2824" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2825">
-      <c r="A2825" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2825" t="inlineStr">
-        <is>
-          <t>cooper steven</t>
-        </is>
-      </c>
-      <c r="C2825" t="n">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2826">
-      <c r="A2826" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2826" t="inlineStr">
-        <is>
-          <t>corberan carlos</t>
-        </is>
-      </c>
-      <c r="C2826" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2827">
-      <c r="A2827" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2827" t="inlineStr">
-        <is>
-          <t>cotterill steve</t>
-        </is>
-      </c>
-      <c r="C2827" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="2828">
-      <c r="A2828" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2828" t="inlineStr">
-        <is>
-          <t>coughlan graham</t>
-        </is>
-      </c>
-      <c r="C2828" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2829">
-      <c r="A2829" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2829" t="inlineStr">
-        <is>
-          <t>cowley danny</t>
-        </is>
-      </c>
-      <c r="C2829" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2830">
-      <c r="A2830" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2830" t="inlineStr">
-        <is>
-          <t>cox neil</t>
-        </is>
-      </c>
-      <c r="C2830" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2831">
-      <c r="A2831" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2831" t="inlineStr">
-        <is>
-          <t>coyle owen</t>
-        </is>
-      </c>
-      <c r="C2831" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2832">
-      <c r="A2832" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2832" t="inlineStr">
-        <is>
-          <t>critchley neil</t>
-        </is>
-      </c>
-      <c r="C2832" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2833">
-      <c r="A2833" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2833" t="inlineStr">
-        <is>
-          <t>crosby andrew</t>
-        </is>
-      </c>
-      <c r="C2833" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2834">
-      <c r="A2834" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2834" t="inlineStr">
-        <is>
-          <t>culverhouse ian</t>
-        </is>
-      </c>
-      <c r="C2834" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2835">
-      <c r="A2835" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2835" t="inlineStr">
-        <is>
-          <t>curle keith</t>
-        </is>
-      </c>
-      <c r="C2835" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2836">
-      <c r="A2836" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2836" t="inlineStr">
-        <is>
-          <t>currie darren</t>
-        </is>
-      </c>
-      <c r="C2836" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2837">
-      <c r="A2837" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2837" t="inlineStr">
-        <is>
-          <t>curtis alan</t>
-        </is>
-      </c>
-      <c r="C2837" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2838">
-      <c r="A2838" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2838" t="inlineStr">
-        <is>
-          <t>dalglish kenny</t>
-        </is>
-      </c>
-      <c r="C2838" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2839">
-      <c r="A2839" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2839" t="inlineStr">
-        <is>
-          <t>danks aaron</t>
-        </is>
-      </c>
-      <c r="C2839" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2840">
-      <c r="A2840" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2840" t="inlineStr">
-        <is>
-          <t>darren way</t>
-        </is>
-      </c>
-      <c r="C2840" t="n">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2841">
-      <c r="A2841" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2841" t="inlineStr">
-        <is>
-          <t>davies billy</t>
-        </is>
-      </c>
-      <c r="C2841" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2842">
-      <c r="A2842" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2842" t="inlineStr">
-        <is>
-          <t>davis kelvin</t>
-        </is>
-      </c>
-      <c r="C2842" t="n">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="2843">
-      <c r="A2843" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2843" t="inlineStr">
-        <is>
-          <t>davis steve</t>
-        </is>
-      </c>
-      <c r="C2843" t="n">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="2844">
-      <c r="A2844" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2844" t="inlineStr">
-        <is>
-          <t>dawes ian</t>
-        </is>
-      </c>
-      <c r="C2844" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2845">
-      <c r="A2845" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2845" t="inlineStr">
-        <is>
-          <t>dawson andy</t>
-        </is>
-      </c>
-      <c r="C2845" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2846">
-      <c r="A2846" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2846" t="inlineStr">
-        <is>
-          <t>de boer frank</t>
-        </is>
-      </c>
-      <c r="C2846" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2847">
-      <c r="A2847" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2847" t="inlineStr">
-        <is>
-          <t>de zerbi roberto</t>
-        </is>
-      </c>
-      <c r="C2847" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2848">
-      <c r="A2848" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2848" t="inlineStr">
-        <is>
-          <t>delap rory</t>
-        </is>
-      </c>
-      <c r="C2848" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2849">
-      <c r="A2849" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2849" t="inlineStr">
-        <is>
-          <t>devaney martin</t>
-        </is>
-      </c>
-      <c r="C2849" t="n">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="2850">
-      <c r="A2850" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2850" t="inlineStr">
-        <is>
-          <t>dewsnip neil</t>
-        </is>
-      </c>
-      <c r="C2850" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2851">
-      <c r="A2851" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2851" t="inlineStr">
-        <is>
-          <t>di canio paolo</t>
-        </is>
-      </c>
-      <c r="C2851" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="2852">
-      <c r="A2852" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2852" t="inlineStr">
-        <is>
-          <t>di matteo roberto</t>
-        </is>
-      </c>
-      <c r="C2852" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="2853">
-      <c r="A2853" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2853" t="inlineStr">
-        <is>
-          <t>di paola dominic</t>
-        </is>
-      </c>
-      <c r="C2853" t="n">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="2854">
-      <c r="A2854" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2854" t="inlineStr">
-        <is>
-          <t>dickov paul</t>
-        </is>
-      </c>
-      <c r="C2854" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="2855">
-      <c r="A2855" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2855" t="inlineStr">
-        <is>
-          <t>dijkhuizen marinus</t>
-        </is>
-      </c>
-      <c r="C2855" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="2856">
-      <c r="A2856" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2856" t="inlineStr">
-        <is>
-          <t>dobbie stephen</t>
-        </is>
-      </c>
-      <c r="C2856" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2857">
-      <c r="A2857" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2857" t="inlineStr">
-        <is>
-          <t>dodds mike</t>
-        </is>
-      </c>
-      <c r="C2857" t="n">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="2858">
-      <c r="A2858" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2858" t="inlineStr">
-        <is>
-          <t>dolan eamonn</t>
-        </is>
-      </c>
-      <c r="C2858" t="n">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="2859">
-      <c r="A2859" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2859" t="inlineStr">
-        <is>
-          <t>doswell paul</t>
-        </is>
-      </c>
-      <c r="C2859" t="n">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="2860">
-      <c r="A2860" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2860" t="inlineStr">
-        <is>
-          <t>dowie iain</t>
-        </is>
-      </c>
-      <c r="C2860" t="n">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="2861">
-      <c r="A2861" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2861" t="inlineStr">
-        <is>
-          <t>downes wally</t>
-        </is>
-      </c>
-      <c r="C2861" t="n">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="2862">
-      <c r="A2862" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2862" t="inlineStr">
-        <is>
-          <t>downing keith</t>
-        </is>
-      </c>
-      <c r="C2862" t="n">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2863">
-      <c r="A2863" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2863" t="inlineStr">
-        <is>
-          <t>duff michael</t>
-        </is>
-      </c>
-      <c r="C2863" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="2864">
-      <c r="A2864" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2864" t="inlineStr">
-        <is>
-          <t>dyche sean</t>
-        </is>
-      </c>
-      <c r="C2864" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="2865">
-      <c r="A2865" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2865" t="inlineStr">
-        <is>
-          <t>eames rossi</t>
-        </is>
-      </c>
-      <c r="C2865" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="2866">
-      <c r="A2866" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2866" t="inlineStr">
-        <is>
-          <t>edinburgh justin</t>
-        </is>
-      </c>
-      <c r="C2866" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2867">
-      <c r="A2867" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2867" t="inlineStr">
-        <is>
-          <t>edwards joe</t>
-        </is>
-      </c>
-      <c r="C2867" t="n">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="2868">
-      <c r="A2868" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2868" t="inlineStr">
-        <is>
-          <t>edwards rob</t>
-        </is>
-      </c>
-      <c r="C2868" t="n">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2869">
-      <c r="A2869" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2869" t="inlineStr">
-        <is>
-          <t>elokobi george</t>
-        </is>
-      </c>
-      <c r="C2869" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="2870">
-      <c r="A2870" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2870" t="inlineStr">
-        <is>
-          <t>emery unai</t>
-        </is>
-      </c>
-      <c r="C2870" t="n">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="2871">
-      <c r="A2871" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2871" t="inlineStr">
-        <is>
-          <t>espirito santo</t>
-        </is>
-      </c>
-      <c r="C2871" t="n">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2872">
-      <c r="A2872" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2872" t="inlineStr">
-        <is>
-          <t>eustace john</t>
-        </is>
-      </c>
-      <c r="C2872" t="n">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="2873">
-      <c r="A2873" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2873" t="inlineStr">
-        <is>
-          <t>evans steve</t>
-        </is>
-      </c>
-      <c r="C2873" t="n">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2874">
-      <c r="A2874" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2874" t="inlineStr">
-        <is>
-          <t>evatt ian</t>
-        </is>
-      </c>
-      <c r="C2874" t="n">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="2875">
-      <c r="A2875" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2875" t="inlineStr">
-        <is>
-          <t>farke daniel</t>
-        </is>
-      </c>
-      <c r="C2875" t="n">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="2876">
-      <c r="A2876" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2876" t="inlineStr">
-        <is>
-          <t>ferguson alex</t>
-        </is>
-      </c>
-      <c r="C2876" t="n">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="2877">
-      <c r="A2877" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2877" t="inlineStr">
-        <is>
-          <t>ferguson barry</t>
-        </is>
-      </c>
-      <c r="C2877" t="n">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="2878">
-      <c r="A2878" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2878" t="inlineStr">
-        <is>
-          <t>ferguson darren</t>
-        </is>
-      </c>
-      <c r="C2878" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="2879">
-      <c r="A2879" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2879" t="inlineStr">
-        <is>
-          <t>ferguson duncan</t>
-        </is>
-      </c>
-      <c r="C2879" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="2880">
-      <c r="A2880" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2880" t="inlineStr">
-        <is>
-          <t>flitcroft david</t>
-        </is>
-      </c>
-      <c r="C2880" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="2881">
-      <c r="A2881" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2881" t="inlineStr">
-        <is>
-          <t>flores quique</t>
-        </is>
-      </c>
-      <c r="C2881" t="n">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="2882">
-      <c r="A2882" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2882" t="inlineStr">
-        <is>
-          <t>flynn michael</t>
-        </is>
-      </c>
-      <c r="C2882" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="2883">
-      <c r="A2883" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2883" t="inlineStr">
-        <is>
-          <t>foster ian</t>
-        </is>
-      </c>
-      <c r="C2883" t="n">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2884">
-      <c r="A2884" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2884" t="inlineStr">
-        <is>
-          <t>fotheringham mark</t>
-        </is>
-      </c>
-      <c r="C2884" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="2885">
-      <c r="A2885" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2885" t="inlineStr">
-        <is>
-          <t>fraeye karel</t>
-        </is>
-      </c>
-      <c r="C2885" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="2886">
-      <c r="A2886" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2886" t="inlineStr">
-        <is>
-          <t>frank thomas</t>
-        </is>
-      </c>
-      <c r="C2886" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="2887">
-      <c r="A2887" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2887" t="inlineStr">
-        <is>
-          <t>freedman dougie</t>
-        </is>
-      </c>
-      <c r="C2887" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="2888">
-      <c r="A2888" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2888" t="inlineStr">
-        <is>
-          <t>gallagher paul</t>
-        </is>
-      </c>
-      <c r="C2888" t="n">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="2889">
-      <c r="A2889" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2889" t="inlineStr">
-        <is>
-          <t>garcia oscar</t>
-        </is>
-      </c>
-      <c r="C2889" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="2890">
-      <c r="A2890" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2890" t="inlineStr">
-        <is>
-          <t>garde remi</t>
-        </is>
-      </c>
-      <c r="C2890" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2891">
-      <c r="A2891" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2891" t="inlineStr">
-        <is>
-          <t>garner ben</t>
-        </is>
-      </c>
-      <c r="C2891" t="n">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="2892">
-      <c r="A2892" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2892" t="inlineStr">
-        <is>
-          <t>garrard luke</t>
-        </is>
-      </c>
-      <c r="C2892" t="n">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="2893">
-      <c r="A2893" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2893" t="inlineStr">
-        <is>
-          <t>gerrard steven</t>
-        </is>
-      </c>
-      <c r="C2893" t="n">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="2894">
-      <c r="A2894" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2894" t="inlineStr">
-        <is>
-          <t>giggs ryan</t>
-        </is>
-      </c>
-      <c r="C2894" t="n">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2895">
-      <c r="A2895" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2895" t="inlineStr">
-        <is>
-          <t>gomes jose</t>
-        </is>
-      </c>
-      <c r="C2895" t="n">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="2896">
-      <c r="A2896" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2896" t="inlineStr">
-        <is>
-          <t>gracia javier</t>
-        </is>
-      </c>
-      <c r="C2896" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="2897">
-      <c r="A2897" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2897" t="inlineStr">
-        <is>
-          <t>grant avram</t>
-        </is>
-      </c>
-      <c r="C2897" t="n">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="2898">
-      <c r="A2898" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2898" t="inlineStr">
-        <is>
-          <t>grant peter</t>
-        </is>
-      </c>
-      <c r="C2898" t="n">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="2899">
-      <c r="A2899" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2899" t="inlineStr">
-        <is>
-          <t>gray matt</t>
-        </is>
-      </c>
-      <c r="C2899" t="n">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="2900">
-      <c r="A2900" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2900" t="inlineStr">
-        <is>
-          <t>gray stuart</t>
-        </is>
-      </c>
-      <c r="C2900" t="n">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="2901">
-      <c r="A2901" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2901" t="inlineStr">
-        <is>
-          <t>grayson simon</t>
-        </is>
-      </c>
-      <c r="C2901" t="n">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="2902">
-      <c r="A2902" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2902" t="inlineStr">
-        <is>
-          <t>guardiola pep</t>
-        </is>
-      </c>
-      <c r="C2902" t="n">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="2903">
-      <c r="A2903" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2903" t="inlineStr">
-        <is>
-          <t>guidolin francesco</t>
-        </is>
-      </c>
-      <c r="C2903" t="n">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="2904">
-      <c r="A2904" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2904" t="inlineStr">
-        <is>
-          <t>harris neil</t>
-        </is>
-      </c>
-      <c r="C2904" t="n">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="2905">
-      <c r="A2905" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2905" t="inlineStr">
-        <is>
-          <t>hart paul</t>
-        </is>
-      </c>
-      <c r="C2905" t="n">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="2906">
-      <c r="A2906" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2906" t="inlineStr">
-        <is>
-          <t>hartley paul</t>
-        </is>
-      </c>
-      <c r="C2906" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="2907">
-      <c r="A2907" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2907" t="inlineStr">
-        <is>
-          <t>hasenhuttl ralph</t>
-        </is>
-      </c>
-      <c r="C2907" t="n">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="2908">
-      <c r="A2908" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2908" t="inlineStr">
-        <is>
-          <t>hasselbaink jimmy floyd</t>
-        </is>
-      </c>
-      <c r="C2908" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="2909">
-      <c r="A2909" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2909" t="inlineStr">
-        <is>
-          <t>hayes anthony</t>
-        </is>
-      </c>
-      <c r="C2909" t="n">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="2910">
-      <c r="A2910" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2910" t="inlineStr">
-        <is>
-          <t>heath billy</t>
-        </is>
-      </c>
-      <c r="C2910" t="n">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="2911">
-      <c r="A2911" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2911" t="inlineStr">
-        <is>
-          <t>heckingbottom paul</t>
-        </is>
-      </c>
-      <c r="C2911" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="2912">
-      <c r="A2912" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2912" t="inlineStr">
-        <is>
-          <t>hiddink guus</t>
-        </is>
-      </c>
-      <c r="C2912" t="n">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="2913">
-      <c r="A2913" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2913" t="inlineStr">
-        <is>
-          <t>hill keith</t>
-        </is>
-      </c>
-      <c r="C2913" t="n">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="2914">
-      <c r="A2914" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2914" t="inlineStr">
-        <is>
-          <t>hill richard</t>
-        </is>
-      </c>
-      <c r="C2914" t="n">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2915">
-      <c r="A2915" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2915" t="inlineStr">
-        <is>
-          <t>hockaday dave</t>
-        </is>
-      </c>
-      <c r="C2915" t="n">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="2916">
-      <c r="A2916" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2916" t="inlineStr">
-        <is>
-          <t>hodgson roy</t>
-        </is>
-      </c>
-      <c r="C2916" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="2917">
-      <c r="A2917" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2917" t="inlineStr">
-        <is>
-          <t>holden dean</t>
-        </is>
-      </c>
-      <c r="C2917" t="n">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="2918">
-      <c r="A2918" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2918" t="inlineStr">
-        <is>
-          <t>holland steve</t>
-        </is>
-      </c>
-      <c r="C2918" t="n">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="2919">
-      <c r="A2919" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2919" t="inlineStr">
-        <is>
-          <t>holloway ian scott</t>
-        </is>
-      </c>
-      <c r="C2919" t="n">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="2920">
-      <c r="A2920" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2920" t="inlineStr">
-        <is>
-          <t>horgan gary</t>
-        </is>
-      </c>
-      <c r="C2920" t="n">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="2921">
-      <c r="A2921" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2921" t="inlineStr">
-        <is>
-          <t>horseman david</t>
-        </is>
-      </c>
-      <c r="C2921" t="n">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="2922">
-      <c r="A2922" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2922" t="inlineStr">
-        <is>
-          <t>houllier gerard</t>
-        </is>
-      </c>
-      <c r="C2922" t="n">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="2923">
-      <c r="A2923" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2923" t="inlineStr">
-        <is>
-          <t>howe eddie</t>
-        </is>
-      </c>
-      <c r="C2923" t="n">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="2924">
-      <c r="A2924" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2924" t="inlineStr">
-        <is>
-          <t>hudson mark</t>
-        </is>
-      </c>
-      <c r="C2924" t="n">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="2925">
-      <c r="A2925" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2925" t="inlineStr">
-        <is>
-          <t>hughes mark</t>
-        </is>
-      </c>
-      <c r="C2925" t="n">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="2926">
-      <c r="A2926" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2926" t="inlineStr">
-        <is>
-          <t>hughton chris</t>
-        </is>
-      </c>
-      <c r="C2926" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="2927">
-      <c r="A2927" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2927" t="inlineStr">
-        <is>
-          <t>hunt noel</t>
-        </is>
-      </c>
-      <c r="C2927" t="n">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="2928">
-      <c r="A2928" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2928" t="inlineStr">
-        <is>
-          <t>hurst paul</t>
-        </is>
-      </c>
-      <c r="C2928" t="n">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="2929">
-      <c r="A2929" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2929" t="inlineStr">
-        <is>
-          <t>hyypia sami</t>
-        </is>
-      </c>
-      <c r="C2929" t="n">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="2930">
-      <c r="A2930" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2930" t="inlineStr">
-        <is>
-          <t>ince paul</t>
-        </is>
-      </c>
-      <c r="C2930" t="n">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="2931">
-      <c r="A2931" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2931" t="inlineStr">
-        <is>
-          <t>iraola andoni</t>
-        </is>
-      </c>
-      <c r="C2931" t="n">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="2932">
-      <c r="A2932" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2932" t="inlineStr">
-        <is>
-          <t>ireland simon</t>
-        </is>
-      </c>
-      <c r="C2932" t="n">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="2933">
-      <c r="A2933" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2933" t="inlineStr">
-        <is>
-          <t>irvine alan</t>
-        </is>
-      </c>
-      <c r="C2933" t="n">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="2934">
-      <c r="A2934" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2934" t="inlineStr">
-        <is>
-          <t>ismael valerien</t>
-        </is>
-      </c>
-      <c r="C2934" t="n">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="2935">
-      <c r="A2935" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2935" t="inlineStr">
-        <is>
-          <t>ivic vladimir</t>
-        </is>
-      </c>
-      <c r="C2935" t="n">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="2936">
-      <c r="A2936" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2936" t="inlineStr">
-        <is>
-          <t>jackett kenny</t>
-        </is>
-      </c>
-      <c r="C2936" t="n">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="2937">
-      <c r="A2937" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2937" t="inlineStr">
-        <is>
-          <t>jackson johnnie</t>
-        </is>
-      </c>
-      <c r="C2937" t="n">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="2938">
-      <c r="A2938" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2938" t="inlineStr">
-        <is>
-          <t>jackson michael</t>
-        </is>
-      </c>
-      <c r="C2938" t="n">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="2939">
-      <c r="A2939" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2939" t="inlineStr">
-        <is>
-          <t>johnson gary</t>
-        </is>
-      </c>
-      <c r="C2939" t="n">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="2940">
-      <c r="A2940" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2940" t="inlineStr">
-        <is>
-          <t>johnson lee</t>
-        </is>
-      </c>
-      <c r="C2940" t="n">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="2941">
-      <c r="A2941" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2941" t="inlineStr">
-        <is>
-          <t>jokanovic slavisa</t>
-        </is>
-      </c>
-      <c r="C2941" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="2942">
-      <c r="A2942" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2942" t="inlineStr">
-        <is>
-          <t>jol martin</t>
-        </is>
-      </c>
-      <c r="C2942" t="n">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="2943">
-      <c r="A2943" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2943" t="inlineStr">
-        <is>
-          <t>jolley michael</t>
-        </is>
-      </c>
-      <c r="C2943" t="n">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="2944">
-      <c r="A2944" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2944" t="inlineStr">
-        <is>
-          <t>jones dave</t>
-        </is>
-      </c>
-      <c r="C2944" t="n">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="2945">
-      <c r="A2945" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2945" t="inlineStr">
-        <is>
-          <t>jones graeme</t>
-        </is>
-      </c>
-      <c r="C2945" t="n">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="2946">
-      <c r="A2946" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2946" t="inlineStr">
-        <is>
-          <t>jones nathan</t>
-        </is>
-      </c>
-      <c r="C2946" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="2947">
-      <c r="A2947" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2947" t="inlineStr">
-        <is>
-          <t>joyce warren</t>
-        </is>
-      </c>
-      <c r="C2947" t="n">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="2948">
-      <c r="A2948" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2948" t="inlineStr">
-        <is>
-          <t>karanka aitor</t>
-        </is>
-      </c>
-      <c r="C2948" t="n">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="2949">
-      <c r="A2949" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2949" t="inlineStr">
-        <is>
-          <t>karanka de la hoz aitor</t>
-        </is>
-      </c>
-      <c r="C2949" t="n">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="2950">
-      <c r="A2950" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2950" t="inlineStr">
-        <is>
-          <t>kean steve</t>
-        </is>
-      </c>
-      <c r="C2950" t="n">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="2951">
-      <c r="A2951" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2951" t="inlineStr">
-        <is>
-          <t>keates dean</t>
-        </is>
-      </c>
-      <c r="C2951" t="n">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="2952">
-      <c r="A2952" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2952" t="inlineStr">
-        <is>
-          <t>keen kevin</t>
-        </is>
-      </c>
-      <c r="C2952" t="n">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="2953">
-      <c r="A2953" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2953" t="inlineStr">
-        <is>
-          <t>kelly rob</t>
-        </is>
-      </c>
-      <c r="C2953" t="n">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="2954">
-      <c r="A2954" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2954" t="inlineStr">
-        <is>
-          <t>kennedy mark</t>
-        </is>
-      </c>
-      <c r="C2954" t="n">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="2955">
-      <c r="A2955" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2955" t="inlineStr">
-        <is>
-          <t>kerslake david</t>
-        </is>
-      </c>
-      <c r="C2955" t="n">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="2956">
-      <c r="A2956" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2956" t="inlineStr">
-        <is>
-          <t>kewell harry</t>
-        </is>
-      </c>
-      <c r="C2956" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="2957">
-      <c r="A2957" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2957" t="inlineStr">
-        <is>
-          <t>kidd brian</t>
-        </is>
-      </c>
-      <c r="C2957" t="n">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="2958">
-      <c r="A2958" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2958" t="inlineStr">
-        <is>
-          <t>klopp jurgen</t>
-        </is>
-      </c>
-      <c r="C2958" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="2959">
-      <c r="A2959" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2959" t="inlineStr">
-        <is>
-          <t>klug bryan</t>
-        </is>
-      </c>
-      <c r="C2959" t="n">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="2960">
-      <c r="A2960" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2960" t="inlineStr">
-        <is>
-          <t>koeman erwin</t>
-        </is>
-      </c>
-      <c r="C2960" t="n">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="2961">
-      <c r="A2961" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2961" t="inlineStr">
-        <is>
-          <t>koeman ronald</t>
-        </is>
-      </c>
-      <c r="C2961" t="n">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="2962">
-      <c r="A2962" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2962" t="inlineStr">
-        <is>
-          <t>kompany vincent</t>
-        </is>
-      </c>
-      <c r="C2962" t="n">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="2963">
-      <c r="A2963" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2963" t="inlineStr">
-        <is>
-          <t>kuhl martin</t>
-        </is>
-      </c>
-      <c r="C2963" t="n">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="2964">
-      <c r="A2964" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2964" t="inlineStr">
-        <is>
-          <t>lage bruno</t>
-        </is>
-      </c>
-      <c r="C2964" t="n">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="2965">
-      <c r="A2965" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2965" t="inlineStr">
-        <is>
-          <t>lambert paul</t>
-        </is>
-      </c>
-      <c r="C2965" t="n">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="2966">
-      <c r="A2966" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2966" t="inlineStr">
-        <is>
-          <t>lamouchi sabri</t>
-        </is>
-      </c>
-      <c r="C2966" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="2967">
-      <c r="A2967" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2967" t="inlineStr">
-        <is>
-          <t>lampard frank</t>
-        </is>
-      </c>
-      <c r="C2967" t="n">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="2968">
-      <c r="A2968" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2968" t="inlineStr">
-        <is>
-          <t>laudrup michael</t>
-        </is>
-      </c>
-      <c r="C2968" t="n">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2969">
-      <c r="A2969" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2969" t="inlineStr">
-        <is>
-          <t>laumann joseph</t>
-        </is>
-      </c>
-      <c r="C2969" t="n">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="2970">
-      <c r="A2970" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2970" t="inlineStr">
-        <is>
-          <t>laws brian</t>
-        </is>
-      </c>
-      <c r="C2970" t="n">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="2971">
-      <c r="A2971" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2971" t="inlineStr">
-        <is>
-          <t>lee graeme</t>
-        </is>
-      </c>
-      <c r="C2971" t="n">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="2972">
-      <c r="A2972" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2972" t="inlineStr">
-        <is>
-          <t>lennon neil</t>
-        </is>
-      </c>
-      <c r="C2972" t="n">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="2973">
-      <c r="A2973" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2973" t="inlineStr">
-        <is>
-          <t>lijnders pepijn</t>
-        </is>
-      </c>
-      <c r="C2973" t="n">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="2974">
-      <c r="A2974" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2974" t="inlineStr">
-        <is>
-          <t>lillo juan manuel</t>
-        </is>
-      </c>
-      <c r="C2974" t="n">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="2975">
-      <c r="A2975" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2975" t="inlineStr">
-        <is>
-          <t>lindsey scott</t>
-        </is>
-      </c>
-      <c r="C2975" t="n">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="2976">
-      <c r="A2976" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2976" t="inlineStr">
-        <is>
-          <t>livermore david</t>
-        </is>
-      </c>
-      <c r="C2976" t="n">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="2977">
-      <c r="A2977" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2977" t="inlineStr">
-        <is>
-          <t>ljungberg fredrik</t>
-        </is>
-      </c>
-      <c r="C2977" t="n">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="2978">
-      <c r="A2978" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2978" t="inlineStr">
-        <is>
-          <t>lomas steve</t>
-        </is>
-      </c>
-      <c r="C2978" t="n">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="2979">
-      <c r="A2979" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2979" t="inlineStr">
-        <is>
-          <t>long ian</t>
-        </is>
-      </c>
-      <c r="C2979" t="n">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="2980">
-      <c r="A2980" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2980" t="inlineStr">
-        <is>
-          <t>lopetegui julen</t>
-        </is>
-      </c>
-      <c r="C2980" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="2981">
-      <c r="A2981" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2981" t="inlineStr">
-        <is>
-          <t>loughlan tony</t>
-        </is>
-      </c>
-      <c r="C2981" t="n">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="2982">
-      <c r="A2982" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2982" t="inlineStr">
-        <is>
-          <t>lovell steve</t>
-        </is>
-      </c>
-      <c r="C2982" t="n">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="2983">
-      <c r="A2983" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2983" t="inlineStr">
-        <is>
-          <t>lowe ryan</t>
-        </is>
-      </c>
-      <c r="C2983" t="n">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="2984">
-      <c r="A2984" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2984" t="inlineStr">
-        <is>
-          <t>luhukay jos</t>
-        </is>
-      </c>
-      <c r="C2984" t="n">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="2985">
-      <c r="A2985" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2985" t="inlineStr">
-        <is>
-          <t>luzon guy</t>
-        </is>
-      </c>
-      <c r="C2985" t="n">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="2986">
-      <c r="A2986" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2986" t="inlineStr">
-        <is>
-          <t>maamria dino</t>
-        </is>
-      </c>
-      <c r="C2986" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="2987">
-      <c r="A2987" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2987" t="inlineStr">
-        <is>
-          <t>macdonald kevin</t>
-        </is>
-      </c>
-      <c r="C2987" t="n">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="2988">
-      <c r="A2988" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2988" t="inlineStr">
-        <is>
-          <t>macfarlane neil</t>
-        </is>
-      </c>
-      <c r="C2988" t="n">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="2989">
-      <c r="A2989" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2989" t="inlineStr">
-        <is>
-          <t>mackay malcolm</t>
-        </is>
-      </c>
-      <c r="C2989" t="n">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="2990">
-      <c r="A2990" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2990" t="inlineStr">
-        <is>
-          <t>magath felix</t>
-        </is>
-      </c>
-      <c r="C2990" t="n">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="2991">
-      <c r="A2991" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2991" t="inlineStr">
-        <is>
-          <t>maldera andrea</t>
-        </is>
-      </c>
-      <c r="C2991" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="2992">
-      <c r="A2992" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2992" t="inlineStr">
-        <is>
-          <t>maloney shaun</t>
-        </is>
-      </c>
-      <c r="C2992" t="n">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="2993">
-      <c r="A2993" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2993" t="inlineStr">
-        <is>
-          <t>mancini roberto</t>
-        </is>
-      </c>
-      <c r="C2993" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="2994">
-      <c r="A2994" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2994" t="inlineStr">
-        <is>
-          <t>manning liam</t>
-        </is>
-      </c>
-      <c r="C2994" t="n">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="2995">
-      <c r="A2995" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2995" t="inlineStr">
-        <is>
-          <t>maresca enzo</t>
-        </is>
-      </c>
-      <c r="C2995" t="n">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="2996">
-      <c r="A2996" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2996" t="inlineStr">
-        <is>
-          <t>marsch jesse</t>
-        </is>
-      </c>
-      <c r="C2996" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="2997">
-      <c r="A2997" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2997" t="inlineStr">
-        <is>
-          <t>marshall scott</t>
-        </is>
-      </c>
-      <c r="C2997" t="n">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="2998">
-      <c r="A2998" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2998" t="inlineStr">
-        <is>
-          <t>martin russell</t>
-        </is>
-      </c>
-      <c r="C2998" t="n">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="2999">
-      <c r="A2999" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B2999" t="inlineStr">
-        <is>
-          <t>martinez roberto</t>
-        </is>
-      </c>
-      <c r="C2999" t="n">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="3000">
-      <c r="A3000" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3000" t="inlineStr">
-        <is>
-          <t>mason ryan</t>
-        </is>
-      </c>
-      <c r="C3000" t="n">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="3001">
-      <c r="A3001" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3001" t="inlineStr">
-        <is>
-          <t>mazzarri walter</t>
-        </is>
-      </c>
-      <c r="C3001" t="n">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="3002">
-      <c r="A3002" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3002" t="inlineStr">
-        <is>
-          <t>mcavoy frankie</t>
-        </is>
-      </c>
-      <c r="C3002" t="n">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="3003">
-      <c r="A3003" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3003" t="inlineStr">
-        <is>
-          <t>mccall stuart</t>
-        </is>
-      </c>
-      <c r="C3003" t="n">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="3004">
-      <c r="A3004" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3004" t="inlineStr">
-        <is>
-          <t>mccann grant</t>
-        </is>
-      </c>
-      <c r="C3004" t="n">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="3005">
-      <c r="A3005" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3005" t="inlineStr">
-        <is>
-          <t>mccarthy mick</t>
-        </is>
-      </c>
-      <c r="C3005" t="n">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="3006">
-      <c r="A3006" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3006" t="inlineStr">
-        <is>
-          <t>mccarthy paddy</t>
-        </is>
-      </c>
-      <c r="C3006" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="3007">
-      <c r="A3007" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3007" t="inlineStr">
-        <is>
-          <t>mcclaren steve</t>
-        </is>
-      </c>
-      <c r="C3007" t="n">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="3008">
-      <c r="A3008" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3008" t="inlineStr">
-        <is>
-          <t>mcdermott brian</t>
-        </is>
-      </c>
-      <c r="C3008" t="n">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="3009">
-      <c r="A3009" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3009" t="inlineStr">
-        <is>
-          <t>mcgreal john</t>
-        </is>
-      </c>
-      <c r="C3009" t="n">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="3010">
-      <c r="A3010" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3010" t="inlineStr">
-        <is>
-          <t>mckenna kieran</t>
-        </is>
-      </c>
-      <c r="C3010" t="n">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="3011">
-      <c r="A3011" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3011" t="inlineStr">
-        <is>
-          <t>mcleish alex</t>
-        </is>
-      </c>
-      <c r="C3011" t="n">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="3012">
-      <c r="A3012" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3012" t="inlineStr">
-        <is>
-          <t>mcmahon daryl</t>
-        </is>
-      </c>
-      <c r="C3012" t="n">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="3013">
-      <c r="A3013" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3013" t="inlineStr">
-        <is>
-          <t>mcnulty jim</t>
-        </is>
-      </c>
-      <c r="C3013" t="n">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="3014">
-      <c r="A3014" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3014" t="inlineStr">
-        <is>
-          <t>mcphillips terry</t>
-        </is>
-      </c>
-      <c r="C3014" t="n">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="3015">
-      <c r="A3015" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3015" t="inlineStr">
-        <is>
-          <t>megson gary</t>
-        </is>
-      </c>
-      <c r="C3015" t="n">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="3016">
-      <c r="A3016" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3016" t="inlineStr">
-        <is>
-          <t>mel pepe</t>
-        </is>
-      </c>
-      <c r="C3016" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="3017">
-      <c r="A3017" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3017" t="inlineStr">
-        <is>
-          <t>mellon micky</t>
-        </is>
-      </c>
-      <c r="C3017" t="n">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="3018">
-      <c r="A3018" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3018" t="inlineStr">
-        <is>
-          <t>meulensteen rene</t>
-        </is>
-      </c>
-      <c r="C3018" t="n">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="3019">
-      <c r="A3019" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3019" t="inlineStr">
-        <is>
-          <t>milanic darko</t>
-        </is>
-      </c>
-      <c r="C3019" t="n">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="3020">
-      <c r="A3020" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3020" t="inlineStr">
-        <is>
-          <t>millen keith</t>
-        </is>
-      </c>
-      <c r="C3020" t="n">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="3021">
-      <c r="A3021" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3021" t="inlineStr">
-        <is>
-          <t>molesley mark</t>
-        </is>
-      </c>
-      <c r="C3021" t="n">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="3022">
-      <c r="A3022" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3022" t="inlineStr">
-        <is>
-          <t>money richard</t>
-        </is>
-      </c>
-      <c r="C3022" t="n">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="3023">
-      <c r="A3023" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3023" t="inlineStr">
-        <is>
-          <t>monk garry</t>
-        </is>
-      </c>
-      <c r="C3023" t="n">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="3024">
-      <c r="A3024" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3024" t="inlineStr">
-        <is>
-          <t>montanier philippe</t>
-        </is>
-      </c>
-      <c r="C3024" t="n">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="3025">
-      <c r="A3025" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3025" t="inlineStr">
-        <is>
-          <t>moore darren</t>
-        </is>
-      </c>
-      <c r="C3025" t="n">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="3026">
-      <c r="A3026" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3026" t="inlineStr">
-        <is>
-          <t>morais jose</t>
-        </is>
-      </c>
-      <c r="C3026" t="n">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="3027">
-      <c r="A3027" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3027" t="inlineStr">
-        <is>
-          <t>morison steve</t>
-        </is>
-      </c>
-      <c r="C3027" t="n">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="3028">
-      <c r="A3028" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3028" t="inlineStr">
-        <is>
-          <t>morris alex</t>
-        </is>
-      </c>
-      <c r="C3028" t="n">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="3029">
-      <c r="A3029" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3029" t="inlineStr">
-        <is>
-          <t>mourinho jose</t>
-        </is>
-      </c>
-      <c r="C3029" t="n">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="3030">
-      <c r="A3030" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3030" t="inlineStr">
-        <is>
-          <t>mousinho john</t>
-        </is>
-      </c>
-      <c r="C3030" t="n">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="3031">
-      <c r="A3031" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3031" t="inlineStr">
-        <is>
-          <t>mowbray tony</t>
-        </is>
-      </c>
-      <c r="C3031" t="n">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="3032">
-      <c r="A3032" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3032" t="inlineStr">
-        <is>
-          <t>moyes david</t>
-        </is>
-      </c>
-      <c r="C3032" t="n">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="3033">
-      <c r="A3033" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3033" t="inlineStr">
-        <is>
-          <t>mullins hayden</t>
-        </is>
-      </c>
-      <c r="C3033" t="n">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="3034">
-      <c r="A3034" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3034" t="inlineStr">
-        <is>
-          <t>murray adam</t>
-        </is>
-      </c>
-      <c r="C3034" t="n">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="3035">
-      <c r="A3035" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3035" t="inlineStr">
-        <is>
-          <t>nancekivell kevin</t>
-        </is>
-      </c>
-      <c r="C3035" t="n">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="3036">
-      <c r="A3036" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3036" t="inlineStr">
-        <is>
-          <t>neil alex</t>
-        </is>
-      </c>
-      <c r="C3036" t="n">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="3037">
-      <c r="A3037" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3037" t="inlineStr">
-        <is>
-          <t>niedzwiecki eddie</t>
-        </is>
-      </c>
-      <c r="C3037" t="n">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="3038">
-      <c r="A3038" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3038" t="inlineStr">
-        <is>
-          <t>nolan kevin</t>
-        </is>
-      </c>
-      <c r="C3038" t="n">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="3039">
-      <c r="A3039" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3039" t="inlineStr">
-        <is>
-          <t>o neil gary</t>
-        </is>
-      </c>
-      <c r="C3039" t="n">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="3040">
-      <c r="A3040" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3040" t="inlineStr">
-        <is>
-          <t>o neill martin</t>
-        </is>
-      </c>
-      <c r="C3040" t="n">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="3041">
-      <c r="A3041" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3041" t="inlineStr">
-        <is>
-          <t>o neill michael</t>
-        </is>
-      </c>
-      <c r="C3041" t="n">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="3042">
-      <c r="A3042" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3042" t="inlineStr">
-        <is>
-          <t>oldfield david</t>
-        </is>
-      </c>
-      <c r="C3042" t="n">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="3043">
-      <c r="A3043" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3043" t="inlineStr">
-        <is>
-          <t>pardew alan</t>
-        </is>
-      </c>
-      <c r="C3043" t="n">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="3044">
-      <c r="A3044" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3044" t="inlineStr">
-        <is>
-          <t>parker scott</t>
-        </is>
-      </c>
-      <c r="C3044" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="3045">
-      <c r="A3045" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3045" t="inlineStr">
-        <is>
-          <t>parkin steve</t>
-        </is>
-      </c>
-      <c r="C3045" t="n">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="3046">
-      <c r="A3046" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3046" t="inlineStr">
-        <is>
-          <t>parkinson phil</t>
-        </is>
-      </c>
-      <c r="C3046" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="3047">
-      <c r="A3047" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3047" t="inlineStr">
-        <is>
-          <t>paunovic veljko</t>
-        </is>
-      </c>
-      <c r="C3047" t="n">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="3048">
-      <c r="A3048" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3048" t="inlineStr">
-        <is>
-          <t>peacock keith</t>
-        </is>
-      </c>
-      <c r="C3048" t="n">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="3049">
-      <c r="A3049" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3049" t="inlineStr">
-        <is>
-          <t>pearce stuart</t>
-        </is>
-      </c>
-      <c r="C3049" t="n">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="3050">
-      <c r="A3050" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3050" t="inlineStr">
-        <is>
-          <t>pearson nigel</t>
-        </is>
-      </c>
-      <c r="C3050" t="n">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="3051">
-      <c r="A3051" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3051" t="inlineStr">
-        <is>
-          <t>peeters bob</t>
-        </is>
-      </c>
-      <c r="C3051" t="n">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="3052">
-      <c r="A3052" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3052" t="inlineStr">
-        <is>
-          <t>pelach narcis</t>
-        </is>
-      </c>
-      <c r="C3052" t="n">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="3053">
-      <c r="A3053" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3053" t="inlineStr">
-        <is>
-          <t>pellegrini manuel</t>
-        </is>
-      </c>
-      <c r="C3053" t="n">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="3054">
-      <c r="A3054" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3054" t="inlineStr">
-        <is>
-          <t>pellegrino mauricio</t>
-        </is>
-      </c>
-      <c r="C3054" t="n">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="3055">
-      <c r="A3055" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3055" t="inlineStr">
-        <is>
-          <t>pemberton john</t>
-        </is>
-      </c>
-      <c r="C3055" t="n">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="3056">
-      <c r="A3056" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3056" t="inlineStr">
-        <is>
-          <t>percovich leo</t>
-        </is>
-      </c>
-      <c r="C3056" t="n">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="3057">
-      <c r="A3057" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3057" t="inlineStr">
-        <is>
-          <t>perez jesus</t>
-        </is>
-      </c>
-      <c r="C3057" t="n">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="3058">
-      <c r="A3058" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3058" t="inlineStr">
-        <is>
-          <t>phelan mike</t>
-        </is>
-      </c>
-      <c r="C3058" t="n">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="3059">
-      <c r="A3059" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3059" t="inlineStr">
-        <is>
-          <t>phillips jimmy</t>
-        </is>
-      </c>
-      <c r="C3059" t="n">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="3060">
-      <c r="A3060" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3060" t="inlineStr">
-        <is>
-          <t>pochettino mauricio</t>
-        </is>
-      </c>
-      <c r="C3060" t="n">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="3061">
-      <c r="A3061" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3061" t="inlineStr">
-        <is>
-          <t>postecoglou ange</t>
-        </is>
-      </c>
-      <c r="C3061" t="n">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="3062">
-      <c r="A3062" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3062" t="inlineStr">
-        <is>
-          <t>potter graham</t>
-        </is>
-      </c>
-      <c r="C3062" t="n">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="3063">
-      <c r="A3063" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3063" t="inlineStr">
-        <is>
-          <t>powell chris</t>
-        </is>
-      </c>
-      <c r="C3063" t="n">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="3064">
-      <c r="A3064" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3064" t="inlineStr">
-        <is>
-          <t>poyet gustavo</t>
-        </is>
-      </c>
-      <c r="C3064" t="n">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="3065">
-      <c r="A3065" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3065" t="inlineStr">
-        <is>
-          <t>pressley steven</t>
-        </is>
-      </c>
-      <c r="C3065" t="n">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="3066">
-      <c r="A3066" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3066" t="inlineStr">
-        <is>
-          <t>puel claude</t>
-        </is>
-      </c>
-      <c r="C3066" t="n">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="3067">
-      <c r="A3067" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3067" t="inlineStr">
-        <is>
-          <t>pulis tony</t>
-        </is>
-      </c>
-      <c r="C3067" t="n">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="3068">
-      <c r="A3068" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3068" t="inlineStr">
-        <is>
-          <t>ramasut tom</t>
-        </is>
-      </c>
-      <c r="C3068" t="n">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="3069">
-      <c r="A3069" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3069" t="inlineStr">
-        <is>
-          <t>ramsey chris</t>
-        </is>
-      </c>
-      <c r="C3069" t="n">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="3070">
-      <c r="A3070" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3070" t="inlineStr">
-        <is>
-          <t>rangnick ralf</t>
-        </is>
-      </c>
-      <c r="C3070" t="n">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="3071">
-      <c r="A3071" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3071" t="inlineStr">
-        <is>
-          <t>ranieri claudio</t>
-        </is>
-      </c>
-      <c r="C3071" t="n">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="3072">
-      <c r="A3072" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3072" t="inlineStr">
-        <is>
-          <t>redfearn neil</t>
-        </is>
-      </c>
-      <c r="C3072" t="n">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="3073">
-      <c r="A3073" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3073" t="inlineStr">
-        <is>
-          <t>redknapp harry</t>
-        </is>
-      </c>
-      <c r="C3073" t="n">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="3074">
-      <c r="A3074" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3074" t="inlineStr">
-        <is>
-          <t>reid steven</t>
-        </is>
-      </c>
-      <c r="C3074" t="n">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="3075">
-      <c r="A3075" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3075" t="inlineStr">
-        <is>
-          <t>richardson leam</t>
-        </is>
-      </c>
-      <c r="C3075" t="n">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="3076">
-      <c r="A3076" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3076" t="inlineStr">
-        <is>
-          <t>ricketts sam</t>
-        </is>
-      </c>
-      <c r="C3076" t="n">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="3077">
-      <c r="A3077" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3077" t="inlineStr">
-        <is>
-          <t>riga jose</t>
-        </is>
-      </c>
-      <c r="C3077" t="n">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="3078">
-      <c r="A3078" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3078" t="inlineStr">
-        <is>
-          <t>roberts osian</t>
-        </is>
-      </c>
-      <c r="C3078" t="n">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="3079">
-      <c r="A3079" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3079" t="inlineStr">
-        <is>
-          <t>roberts tony</t>
-        </is>
-      </c>
-      <c r="C3079" t="n">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="3080">
-      <c r="A3080" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3080" t="inlineStr">
-        <is>
-          <t>robins mark</t>
-        </is>
-      </c>
-      <c r="C3080" t="n">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="3081">
-      <c r="A3081" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3081" t="inlineStr">
-        <is>
-          <t>robinson karl</t>
-        </is>
-      </c>
-      <c r="C3081" t="n">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="3082">
-      <c r="A3082" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3082" t="inlineStr">
-        <is>
-          <t>robinson mark</t>
-        </is>
-      </c>
-      <c r="C3082" t="n">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="3083">
-      <c r="A3083" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3083" t="inlineStr">
-        <is>
-          <t>robinson stephen</t>
-        </is>
-      </c>
-      <c r="C3083" t="n">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="3084">
-      <c r="A3084" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3084" t="inlineStr">
-        <is>
-          <t>rodgers brendan</t>
-        </is>
-      </c>
-      <c r="C3084" t="n">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="3085">
-      <c r="A3085" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3085" t="inlineStr">
-        <is>
-          <t>rohl danny</t>
-        </is>
-      </c>
-      <c r="C3085" t="n">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="3086">
-      <c r="A3086" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3086" t="inlineStr">
-        <is>
-          <t>rooney wayne</t>
-        </is>
-      </c>
-      <c r="C3086" t="n">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="3087">
-      <c r="A3087" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3087" t="inlineStr">
-        <is>
-          <t>rosenior liam</t>
-        </is>
-      </c>
-      <c r="C3087" t="n">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="3088">
-      <c r="A3088" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3088" t="inlineStr">
-        <is>
-          <t>rosler uwe</t>
-        </is>
-      </c>
-      <c r="C3088" t="n">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="3089">
-      <c r="A3089" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3089" t="inlineStr">
-        <is>
-          <t>ross jack</t>
-        </is>
-      </c>
-      <c r="C3089" t="n">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="3090">
-      <c r="A3090" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3090" t="inlineStr">
-        <is>
-          <t>rowberry james</t>
-        </is>
-      </c>
-      <c r="C3090" t="n">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="3091">
-      <c r="A3091" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3091" t="inlineStr">
-        <is>
-          <t>rowe james</t>
-        </is>
-      </c>
-      <c r="C3091" t="n">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="3092">
-      <c r="A3092" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3092" t="inlineStr">
-        <is>
-          <t>rowett gary</t>
-        </is>
-      </c>
-      <c r="C3092" t="n">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="3093">
-      <c r="A3093" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3093" t="inlineStr">
-        <is>
-          <t>russell martin</t>
-        </is>
-      </c>
-      <c r="C3093" t="n">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="3094">
-      <c r="A3094" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3094" t="inlineStr">
-        <is>
-          <t>sadler mathew john</t>
-        </is>
-      </c>
-      <c r="C3094" t="n">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="3095">
-      <c r="A3095" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3095" t="inlineStr">
-        <is>
-          <t>sannino giuseppe</t>
-        </is>
-      </c>
-      <c r="C3095" t="n">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="3096">
-      <c r="A3096" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3096" t="inlineStr">
-        <is>
-          <t>sarri maurizio</t>
-        </is>
-      </c>
-      <c r="C3096" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="3097">
-      <c r="A3097" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3097" t="inlineStr">
-        <is>
-          <t>schofield danny</t>
-        </is>
-      </c>
-      <c r="C3097" t="n">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="3098">
-      <c r="A3098" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3098" t="inlineStr">
-        <is>
-          <t>schopp markus</t>
-        </is>
-      </c>
-      <c r="C3098" t="n">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="3099">
-      <c r="A3099" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3099" t="inlineStr">
-        <is>
-          <t>schumacher steven</t>
-        </is>
-      </c>
-      <c r="C3099" t="n">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="3100">
-      <c r="A3100" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3100" t="inlineStr">
-        <is>
-          <t>selles ruben</t>
-        </is>
-      </c>
-      <c r="C3100" t="n">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="3101">
-      <c r="A3101" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3101" t="inlineStr">
-        <is>
-          <t>shakespeare craig</t>
-        </is>
-      </c>
-      <c r="C3101" t="n">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="3102">
-      <c r="A3102" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3102" t="inlineStr">
-        <is>
-          <t>shan james</t>
-        </is>
-      </c>
-      <c r="C3102" t="n">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="3103">
-      <c r="A3103" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3103" t="inlineStr">
-        <is>
-          <t>sheehan alan</t>
-        </is>
-      </c>
-      <c r="C3103" t="n">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="3104">
-      <c r="A3104" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3104" t="inlineStr">
-        <is>
-          <t>sherwood tim</t>
-        </is>
-      </c>
-      <c r="C3104" t="n">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="3105">
-      <c r="A3105" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3105" t="inlineStr">
-        <is>
-          <t>siewert jan</t>
-        </is>
-      </c>
-      <c r="C3105" t="n">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="3106">
-      <c r="A3106" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3106" t="inlineStr">
-        <is>
-          <t>silva marco</t>
-        </is>
-      </c>
-      <c r="C3106" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="3107">
-      <c r="A3107" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3107" t="inlineStr">
-        <is>
-          <t>simpson paul</t>
-        </is>
-      </c>
-      <c r="C3107" t="n">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="3108">
-      <c r="A3108" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3108" t="inlineStr">
-        <is>
-          <t>skubala michael</t>
-        </is>
-      </c>
-      <c r="C3108" t="n">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="3109">
-      <c r="A3109" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3109" t="inlineStr">
-        <is>
-          <t>slade russell</t>
-        </is>
-      </c>
-      <c r="C3109" t="n">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="3110">
-      <c r="A3110" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3110" t="inlineStr">
-        <is>
-          <t>slutski leonid</t>
-        </is>
-      </c>
-      <c r="C3110" t="n">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="3111">
-      <c r="A3111" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3111" t="inlineStr">
-        <is>
-          <t>smith ben</t>
-        </is>
-      </c>
-      <c r="C3111" t="n">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="3112">
-      <c r="A3112" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3112" t="inlineStr">
-        <is>
-          <t>smith dean</t>
-        </is>
-      </c>
-      <c r="C3112" t="n">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="3113">
-      <c r="A3113" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3113" t="inlineStr">
-        <is>
-          <t>solskjaer ole gunnar</t>
-        </is>
-      </c>
-      <c r="C3113" t="n">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="3114">
-      <c r="A3114" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3114" t="inlineStr">
-        <is>
-          <t>spencer day</t>
-        </is>
-      </c>
-      <c r="C3114" t="n">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="3115">
-      <c r="A3115" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3115" t="inlineStr">
-        <is>
-          <t>spooner steve</t>
-        </is>
-      </c>
-      <c r="C3115" t="n">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="3116">
-      <c r="A3116" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3116" t="inlineStr">
-        <is>
-          <t>stam jaap</t>
-        </is>
-      </c>
-      <c r="C3116" t="n">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="3117">
-      <c r="A3117" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3117" t="inlineStr">
-        <is>
-          <t>stellini cristian</t>
-        </is>
-      </c>
-      <c r="C3117" t="n">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="3118">
-      <c r="A3118" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3118" t="inlineStr">
-        <is>
-          <t>stendel daniel</t>
-        </is>
-      </c>
-      <c r="C3118" t="n">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="3119">
-      <c r="A3119" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3119" t="inlineStr">
-        <is>
-          <t>still john</t>
-        </is>
-      </c>
-      <c r="C3119" t="n">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="3120">
-      <c r="A3120" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3120" t="inlineStr">
-        <is>
-          <t>stockdale robbie</t>
-        </is>
-      </c>
-      <c r="C3120" t="n">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="3121">
-      <c r="A3121" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3121" t="inlineStr">
-        <is>
-          <t>struber gerhard</t>
-        </is>
-      </c>
-      <c r="C3121" t="n">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="3122">
-      <c r="A3122" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3122" t="inlineStr">
-        <is>
-          <t>stubbs alan</t>
-        </is>
-      </c>
-      <c r="C3122" t="n">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="3123">
-      <c r="A3123" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3123" t="inlineStr">
-        <is>
-          <t>stuivenberg albert</t>
-        </is>
-      </c>
-      <c r="C3123" t="n">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="3124">
-      <c r="A3124" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3124" t="inlineStr">
-        <is>
-          <t>symons kit</t>
-        </is>
-      </c>
-      <c r="C3124" t="n">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="3125">
-      <c r="A3125" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3125" t="inlineStr">
-        <is>
-          <t>taylor matt</t>
-        </is>
-      </c>
-      <c r="C3125" t="n">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="3126">
-      <c r="A3126" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3126" t="inlineStr">
-        <is>
-          <t>taylor matthew</t>
-        </is>
-      </c>
-      <c r="C3126" t="n">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="3127">
-      <c r="A3127" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3127" t="inlineStr">
-        <is>
-          <t>ten hag erik</t>
-        </is>
-      </c>
-      <c r="C3127" t="n">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="3128">
-      <c r="A3128" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3128" t="inlineStr">
-        <is>
-          <t>thompson neil</t>
-        </is>
-      </c>
-      <c r="C3128" t="n">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="3129">
-      <c r="A3129" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3129" t="inlineStr">
-        <is>
-          <t>thompson steven</t>
-        </is>
-      </c>
-      <c r="C3129" t="n">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="3130">
-      <c r="A3130" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3130" t="inlineStr">
-        <is>
-          <t>tindall jason</t>
-        </is>
-      </c>
-      <c r="C3130" t="n">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="3131">
-      <c r="A3131" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3131" t="inlineStr">
-        <is>
-          <t>tisdale paul</t>
-        </is>
-      </c>
-      <c r="C3131" t="n">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="3132">
-      <c r="A3132" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3132" t="inlineStr">
-        <is>
-          <t>tomasson jon dahl</t>
-        </is>
-      </c>
-      <c r="C3132" t="n">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="3133">
-      <c r="A3133" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3133" t="inlineStr">
-        <is>
-          <t>toure kolo</t>
-        </is>
-      </c>
-      <c r="C3133" t="n">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="3134">
-      <c r="A3134" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3134" t="inlineStr">
-        <is>
-          <t>trollope paul</t>
-        </is>
-      </c>
-      <c r="C3134" t="n">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="3135">
-      <c r="A3135" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3135" t="inlineStr">
-        <is>
-          <t>tuchel thomas</t>
-        </is>
-      </c>
-      <c r="C3135" t="n">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="3136">
-      <c r="A3136" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3136" t="inlineStr">
-        <is>
-          <t>unsworth david</t>
-        </is>
-      </c>
-      <c r="C3136" t="n">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="3137">
-      <c r="A3137" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3137" t="inlineStr">
-        <is>
-          <t>van der gaag mitchell</t>
-        </is>
-      </c>
-      <c r="C3137" t="n">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="3138">
-      <c r="A3138" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3138" t="inlineStr">
-        <is>
-          <t>van gaal louis</t>
-        </is>
-      </c>
-      <c r="C3138" t="n">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="3139">
-      <c r="A3139" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3139" t="inlineStr">
-        <is>
-          <t>venus mark</t>
-        </is>
-      </c>
-      <c r="C3139" t="n">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="3140">
-      <c r="A3140" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3140" t="inlineStr">
-        <is>
-          <t>vermiglio jamie</t>
-        </is>
-      </c>
-      <c r="C3140" t="n">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="3141">
-      <c r="A3141" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3141" t="inlineStr">
-        <is>
-          <t>vieira patrick</t>
-        </is>
-      </c>
-      <c r="C3141" t="n">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="3142">
-      <c r="A3142" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3142" t="inlineStr">
-        <is>
-          <t>villas boas andre</t>
-        </is>
-      </c>
-      <c r="C3142" t="n">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="3143">
-      <c r="A3143" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3143" t="inlineStr">
-        <is>
-          <t>wagner david</t>
-        </is>
-      </c>
-      <c r="C3143" t="n">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="3144">
-      <c r="A3144" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3144" t="inlineStr">
-        <is>
-          <t>warburton mark</t>
-        </is>
-      </c>
-      <c r="C3144" t="n">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="3145">
-      <c r="A3145" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3145" t="inlineStr">
-        <is>
-          <t>warne paul</t>
-        </is>
-      </c>
-      <c r="C3145" t="n">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="3146">
-      <c r="A3146" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3146" t="inlineStr">
-        <is>
-          <t>warnock neil</t>
-        </is>
-      </c>
-      <c r="C3146" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="3147">
-      <c r="A3147" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3147" t="inlineStr">
-        <is>
-          <t>wassall darren</t>
-        </is>
-      </c>
-      <c r="C3147" t="n">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="3148">
-      <c r="A3148" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3148" t="inlineStr">
-        <is>
-          <t>weaver simon</t>
-        </is>
-      </c>
-      <c r="C3148" t="n">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="3149">
-      <c r="A3149" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3149" t="inlineStr">
-        <is>
-          <t>wellens richie</t>
-        </is>
-      </c>
-      <c r="C3149" t="n">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="3150">
-      <c r="A3150" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3150" t="inlineStr">
-        <is>
-          <t>wenger arsene</t>
-        </is>
-      </c>
-      <c r="C3150" t="n">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="3151">
-      <c r="A3151" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3151" t="inlineStr">
-        <is>
-          <t>westley graham</t>
-        </is>
-      </c>
-      <c r="C3151" t="n">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="3152">
-      <c r="A3152" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3152" t="inlineStr">
-        <is>
-          <t>whitehead dean</t>
-        </is>
-      </c>
-      <c r="C3152" t="n">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="3153">
-      <c r="A3153" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3153" t="inlineStr">
-        <is>
-          <t>widdrington tommy</t>
-        </is>
-      </c>
-      <c r="C3153" t="n">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="3154">
-      <c r="A3154" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3154" t="inlineStr">
-        <is>
-          <t>wild pete</t>
-        </is>
-      </c>
-      <c r="C3154" t="n">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="3155">
-      <c r="A3155" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3155" t="inlineStr">
-        <is>
-          <t>wilder chris</t>
-        </is>
-      </c>
-      <c r="C3155" t="n">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="3156">
-      <c r="A3156" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3156" t="inlineStr">
-        <is>
-          <t>williams luke</t>
-        </is>
-      </c>
-      <c r="C3156" t="n">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="3157">
-      <c r="A3157" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3157" t="inlineStr">
-        <is>
-          <t>williams paul</t>
-        </is>
-      </c>
-      <c r="C3157" t="n">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="3158">
-      <c r="A3158" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3158" t="inlineStr">
-        <is>
-          <t>wilson danny</t>
-        </is>
-      </c>
-      <c r="C3158" t="n">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="3159">
-      <c r="A3159" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3159" t="inlineStr">
-        <is>
-          <t>woan ian</t>
-        </is>
-      </c>
-      <c r="C3159" t="n">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="3160">
-      <c r="A3160" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3160" t="inlineStr">
-        <is>
-          <t>wood neil</t>
-        </is>
-      </c>
-      <c r="C3160" t="n">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="3161">
-      <c r="A3161" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3161" t="inlineStr">
-        <is>
-          <t>woodgate jonathan</t>
-        </is>
-      </c>
-      <c r="C3161" t="n">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="3162">
-      <c r="A3162" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3162" t="inlineStr">
-        <is>
-          <t>worthington jon</t>
-        </is>
-      </c>
-      <c r="C3162" t="n">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="3163">
-      <c r="A3163" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3163" t="inlineStr">
-        <is>
-          <t>xisco</t>
-        </is>
-      </c>
-      <c r="C3163" t="n">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="3164">
-      <c r="A3164" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3164" t="inlineStr">
-        <is>
-          <t>yates mark</t>
-        </is>
-      </c>
-      <c r="C3164" t="n">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="3165">
-      <c r="A3165" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3165" t="inlineStr">
-        <is>
-          <t>yems john</t>
-        </is>
-      </c>
-      <c r="C3165" t="n">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="3166">
-      <c r="A3166" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3166" t="inlineStr">
-        <is>
-          <t>young lewis</t>
-        </is>
-      </c>
-      <c r="C3166" t="n">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="3167">
-      <c r="A3167" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3167" t="inlineStr">
-        <is>
-          <t>young neil</t>
-        </is>
-      </c>
-      <c r="C3167" t="n">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="3168">
-      <c r="A3168" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3168" t="inlineStr">
-        <is>
-          <t>young scott</t>
-        </is>
-      </c>
-      <c r="C3168" t="n">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="3169">
-      <c r="A3169" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3169" t="inlineStr">
-        <is>
-          <t>zenga walter</t>
-        </is>
-      </c>
-      <c r="C3169" t="n">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="3170">
-      <c r="A3170" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="B3170" t="inlineStr">
-        <is>
-          <t>zola gianfranco</t>
-        </is>
-      </c>
-      <c r="C3170" t="n">
-        <v>424</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
